--- a/public/downloads/PasumarthiDoubleLayer2023.xlsx
+++ b/public/downloads/PasumarthiDoubleLayer2023.xlsx
@@ -1590,16 +1590,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4803171472507405</v>
+        <v>-0.5193862365222515</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1050285870061006</v>
+        <v>0.09200555724893029</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08041150137121249</v>
+        <v>0.07259768351691029</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0688524423385168</v>
+        <v>-0.1167530289322229</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -3415,7 +3415,7 @@
         <v>0.08449854855862544</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0899960217845924</v>
+        <v>0.08041590446585119</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4347543126896423</v>
+        <v>-0.429553352561916</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -9829,16 +9829,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4493861428454634</v>
+        <v>-0.4374203335937619</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.311449833826663</v>
+        <v>0.3114498338266631</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.311449833826663</v>
+        <v>0.3114498338266631</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -10712,13 +10712,13 @@
         <v>13.1578947368421</v>
       </c>
       <c r="H3" s="4">
-        <v>1.387636359623177</v>
+        <v>1.385167906096812</v>
       </c>
       <c r="I3" s="4">
-        <v>0.9597371208378009</v>
+        <v>0.9580000609488774</v>
       </c>
       <c r="J3" s="4">
-        <v>1.128928032340666</v>
+        <v>1.131372851740851</v>
       </c>
       <c r="K3" s="4">
         <v>81.51360544217684</v>
@@ -10918,7 +10918,7 @@
         <v>0.4614266121282145</v>
       </c>
       <c r="J7" s="4">
-        <v>0.4542015285218792</v>
+        <v>0.4548725468207283</v>
       </c>
       <c r="K7" s="4">
         <v>82.78195488721799</v>
@@ -10962,13 +10962,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.931863392909743</v>
+        <v>0.9298071250533477</v>
       </c>
       <c r="I8" s="4">
-        <v>0.7570220622475031</v>
+        <v>0.7557617690451963</v>
       </c>
       <c r="J8" s="4">
-        <v>0.7511998778411498</v>
+        <v>0.753431145270878</v>
       </c>
       <c r="K8" s="4">
         <v>77.78195488721816</v>
@@ -11065,10 +11065,10 @@
         <v>0.3773246842292513</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3345194890289246</v>
+        <v>0.3329228028091344</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3335987668901919</v>
+        <v>0.3339573987271008</v>
       </c>
       <c r="K10" s="4">
         <v>86.60401002506248</v>
@@ -13115,16 +13115,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.7412650291822501</v>
+        <v>-0.7881656461831881</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1122677769582272</v>
+        <v>0.09663423795791459</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1093031429609982</v>
+        <v>0.09992301956081065</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -16765,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.09994520063749708</v>
+        <v>-0.1126945483156305</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
